--- a/backend/data/financials_by_company/0953.HK.xlsx
+++ b/backend/data/financials_by_company/0953.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT5"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,56 +652,24 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-2171000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3836000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-8684000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-8684000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-5779000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3761000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>29693000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-4848000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-8609000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>11820000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>608000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>12428000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>734000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-5779000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>65058000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>1419610000</v>
       </c>
@@ -709,136 +677,88 @@
         <v>1419610000</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0041</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>-5779000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-5779000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-5779000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5269000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-11048000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-11048000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1831000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-9217000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1283000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-8684000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-143000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>8827000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>11820000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>608000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>12428000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-13423000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>35365000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>35471000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1906000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>33565000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>21942000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>29693000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>51635000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>51635000</v>
-      </c>
+        <v>0.0116</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-3419500</v>
+        <v>-1925750</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>11061000</v>
+        <v>4311000</v>
       </c>
       <c r="E3" t="n">
-        <v>-13678000</v>
+        <v>-7703000</v>
       </c>
       <c r="F3" t="n">
-        <v>-13678000</v>
+        <v>-7703000</v>
       </c>
       <c r="G3" t="n">
-        <v>-2898000</v>
+        <v>-302000</v>
       </c>
       <c r="H3" t="n">
-        <v>4119000</v>
+        <v>2624000</v>
       </c>
       <c r="I3" t="n">
-        <v>34251000</v>
+        <v>110738000</v>
       </c>
       <c r="J3" t="n">
-        <v>-2617000</v>
+        <v>-3392000</v>
       </c>
       <c r="K3" t="n">
-        <v>-6736000</v>
+        <v>-6016000</v>
       </c>
       <c r="L3" t="n">
-        <v>9489000</v>
+        <v>3363000</v>
       </c>
       <c r="M3" t="n">
-        <v>816000</v>
+        <v>624000</v>
       </c>
       <c r="N3" t="n">
-        <v>10305000</v>
+        <v>3987000</v>
       </c>
       <c r="O3" t="n">
-        <v>7360500</v>
+        <v>5475250</v>
       </c>
       <c r="P3" t="n">
-        <v>-2898000</v>
+        <v>-302000</v>
       </c>
       <c r="Q3" t="n">
-        <v>70711000</v>
+        <v>152949000</v>
       </c>
       <c r="R3" t="n">
         <v>1419610000</v>
@@ -847,138 +767,138 @@
         <v>1419610000</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.002</v>
+        <v>-0.0002</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.002</v>
+        <v>-0.0002</v>
       </c>
       <c r="V3" t="n">
-        <v>-2898000</v>
+        <v>-302000</v>
       </c>
       <c r="W3" t="n">
-        <v>-2898000</v>
+        <v>-302000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2898000</v>
+        <v>-302000</v>
       </c>
       <c r="Z3" t="n">
-        <v>4819000</v>
+        <v>7223000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-7717000</v>
+        <v>-7525000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-7717000</v>
+        <v>-7525000</v>
       </c>
       <c r="AC3" t="n">
-        <v>165000</v>
+        <v>885000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-7552000</v>
+        <v>-6640000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2717000</v>
+        <v>1516000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-13678000</v>
+        <v>-7703000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-980000</v>
+        <v>-148000</v>
       </c>
       <c r="AH3" t="n">
-        <v>14658000</v>
+        <v>7851000</v>
       </c>
       <c r="AI3" t="n">
-        <v>9489000</v>
+        <v>3363000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>816000</v>
+        <v>624000</v>
       </c>
       <c r="AK3" t="n">
-        <v>10305000</v>
+        <v>3987000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-6175000</v>
+        <v>8102000</v>
       </c>
       <c r="AM3" t="n">
-        <v>36460000</v>
+        <v>42211000</v>
       </c>
       <c r="AN3" t="n">
-        <v>36642000</v>
+        <v>42875000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1456000</v>
+        <v>5550000</v>
       </c>
       <c r="AP3" t="n">
-        <v>35186000</v>
+        <v>37325000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>30285000</v>
+        <v>50313000</v>
       </c>
       <c r="AR3" t="n">
-        <v>34251000</v>
+        <v>110738000</v>
       </c>
       <c r="AS3" t="n">
-        <v>64536000</v>
+        <v>161051000</v>
       </c>
       <c r="AT3" t="n">
-        <v>64536000</v>
+        <v>161051000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1925750</v>
+        <v>-3419500</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>4311000</v>
+        <v>11061000</v>
       </c>
       <c r="E4" t="n">
-        <v>-7703000</v>
+        <v>-13678000</v>
       </c>
       <c r="F4" t="n">
-        <v>-7703000</v>
+        <v>-13678000</v>
       </c>
       <c r="G4" t="n">
-        <v>-302000</v>
+        <v>-2898000</v>
       </c>
       <c r="H4" t="n">
-        <v>2624000</v>
+        <v>4119000</v>
       </c>
       <c r="I4" t="n">
-        <v>110738000</v>
+        <v>34251000</v>
       </c>
       <c r="J4" t="n">
-        <v>-3392000</v>
+        <v>-2617000</v>
       </c>
       <c r="K4" t="n">
-        <v>-6016000</v>
+        <v>-6736000</v>
       </c>
       <c r="L4" t="n">
-        <v>3363000</v>
+        <v>9489000</v>
       </c>
       <c r="M4" t="n">
-        <v>624000</v>
+        <v>816000</v>
       </c>
       <c r="N4" t="n">
-        <v>3987000</v>
+        <v>10305000</v>
       </c>
       <c r="O4" t="n">
-        <v>5475250</v>
+        <v>7360500</v>
       </c>
       <c r="P4" t="n">
-        <v>-302000</v>
+        <v>-2898000</v>
       </c>
       <c r="Q4" t="n">
-        <v>152949000</v>
+        <v>70711000</v>
       </c>
       <c r="R4" t="n">
         <v>1419610000</v>
@@ -987,138 +907,138 @@
         <v>1419610000</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0002</v>
+        <v>-0.002</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0002</v>
+        <v>-0.002</v>
       </c>
       <c r="V4" t="n">
-        <v>-302000</v>
+        <v>-2898000</v>
       </c>
       <c r="W4" t="n">
-        <v>-302000</v>
+        <v>-2898000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-302000</v>
+        <v>-2898000</v>
       </c>
       <c r="Z4" t="n">
-        <v>7223000</v>
+        <v>4819000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-7525000</v>
+        <v>-7717000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-7525000</v>
+        <v>-7717000</v>
       </c>
       <c r="AC4" t="n">
-        <v>885000</v>
+        <v>165000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-6640000</v>
+        <v>-7552000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1516000</v>
+        <v>2717000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-7703000</v>
+        <v>-13678000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-148000</v>
+        <v>-980000</v>
       </c>
       <c r="AH4" t="n">
-        <v>7851000</v>
+        <v>14658000</v>
       </c>
       <c r="AI4" t="n">
-        <v>3363000</v>
+        <v>9489000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>624000</v>
+        <v>816000</v>
       </c>
       <c r="AK4" t="n">
-        <v>3987000</v>
+        <v>10305000</v>
       </c>
       <c r="AL4" t="n">
-        <v>8102000</v>
+        <v>-6175000</v>
       </c>
       <c r="AM4" t="n">
-        <v>42211000</v>
+        <v>36460000</v>
       </c>
       <c r="AN4" t="n">
-        <v>42875000</v>
+        <v>36642000</v>
       </c>
       <c r="AO4" t="n">
-        <v>5550000</v>
+        <v>1456000</v>
       </c>
       <c r="AP4" t="n">
-        <v>37325000</v>
+        <v>35186000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>50313000</v>
+        <v>30285000</v>
       </c>
       <c r="AR4" t="n">
-        <v>110738000</v>
+        <v>34251000</v>
       </c>
       <c r="AS4" t="n">
-        <v>161051000</v>
+        <v>64536000</v>
       </c>
       <c r="AT4" t="n">
-        <v>161051000</v>
+        <v>64536000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-6519245.432056</v>
+        <v>-2171000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.329022</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>45514000</v>
+        <v>3836000</v>
       </c>
       <c r="E5" t="n">
-        <v>-19814000</v>
+        <v>-8684000</v>
       </c>
       <c r="F5" t="n">
-        <v>-19814000</v>
+        <v>-8684000</v>
       </c>
       <c r="G5" t="n">
-        <v>16403000</v>
+        <v>-5779000</v>
       </c>
       <c r="H5" t="n">
-        <v>2336000</v>
+        <v>3761000</v>
       </c>
       <c r="I5" t="n">
-        <v>134638000</v>
+        <v>29693000</v>
       </c>
       <c r="J5" t="n">
-        <v>25700000</v>
+        <v>-4848000</v>
       </c>
       <c r="K5" t="n">
-        <v>23364000</v>
+        <v>-8609000</v>
       </c>
       <c r="L5" t="n">
-        <v>1814000</v>
+        <v>11820000</v>
       </c>
       <c r="M5" t="n">
-        <v>323000</v>
+        <v>608000</v>
       </c>
       <c r="N5" t="n">
-        <v>2137000</v>
+        <v>12428000</v>
       </c>
       <c r="O5" t="n">
-        <v>29697754.567944</v>
+        <v>734000</v>
       </c>
       <c r="P5" t="n">
-        <v>16403000</v>
+        <v>-5779000</v>
       </c>
       <c r="Q5" t="n">
-        <v>177920000</v>
+        <v>65058000</v>
       </c>
       <c r="R5" t="n">
         <v>1419610000</v>
@@ -1127,83 +1047,213 @@
         <v>1419610000</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0116</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.0116</v>
-      </c>
+        <v>-0.0041</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>16403000</v>
+        <v>-5779000</v>
       </c>
       <c r="W5" t="n">
-        <v>16403000</v>
+        <v>-5779000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>16403000</v>
+        <v>-5779000</v>
       </c>
       <c r="Z5" t="n">
-        <v>943000</v>
+        <v>5269000</v>
       </c>
       <c r="AA5" t="n">
-        <v>15460000</v>
+        <v>-11048000</v>
       </c>
       <c r="AB5" t="n">
-        <v>15460000</v>
+        <v>-11048000</v>
       </c>
       <c r="AC5" t="n">
-        <v>7581000</v>
+        <v>1831000</v>
       </c>
       <c r="AD5" t="n">
-        <v>23041000</v>
+        <v>-9217000</v>
       </c>
       <c r="AE5" t="n">
-        <v>934000</v>
+        <v>1283000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-19814000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>-8684000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-143000</v>
+      </c>
       <c r="AH5" t="n">
-        <v>19814000</v>
+        <v>8827000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1814000</v>
+        <v>11820000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>323000</v>
+        <v>608000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2137000</v>
+        <v>12428000</v>
       </c>
       <c r="AL5" t="n">
-        <v>37598000</v>
+        <v>-13423000</v>
       </c>
       <c r="AM5" t="n">
-        <v>43282000</v>
+        <v>35365000</v>
       </c>
       <c r="AN5" t="n">
-        <v>43527000</v>
+        <v>35471000</v>
       </c>
       <c r="AO5" t="n">
-        <v>7590000</v>
+        <v>1906000</v>
       </c>
       <c r="AP5" t="n">
-        <v>35937000</v>
+        <v>33565000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>80880000</v>
+        <v>21942000</v>
       </c>
       <c r="AR5" t="n">
-        <v>134638000</v>
+        <v>29693000</v>
       </c>
       <c r="AS5" t="n">
-        <v>215518000</v>
+        <v>51635000</v>
       </c>
       <c r="AT5" t="n">
-        <v>215518000</v>
+        <v>51635000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-8835500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24613000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-35342000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-35342000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-14211000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2931000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>114714000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-10729000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-13660000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7098000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>379000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7477000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>12295500</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-14211000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>140567000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-14211000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-14211000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-14211000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>292000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-14503000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-14503000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>464000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-14039000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>949000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-35342000</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>35342000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>7098000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>379000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>7477000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>13155000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>25853000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>25950000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>374000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>25576000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>39008000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>114714000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>153722000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>153722000</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF5"/>
+  <dimension ref="A1:BF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1509,179 +1559,75 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1419610000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1419610000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7341000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>429358000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>435220000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>403021000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>429358000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2629000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>430508000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>430508000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>406792000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-23716000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>430508000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-458764000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>750821000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>12322000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>12322000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>105767000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>746000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>746000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>746000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>105021000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>6595000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1883000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4712000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>33639000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>14960000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>292000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>18387000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>512559000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4517000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>105000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>52000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>52000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1150000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>28616000</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>3210000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-4698000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7908000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>5701000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2207000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>508042000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>73946000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>11569000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>44294000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4833000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-14030000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>18863000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>373400000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>55250000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>318150000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>289900000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>28250000</v>
-      </c>
+        <v>3491000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>8717000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1419610000</v>
@@ -1690,40 +1636,40 @@
         <v>1419610000</v>
       </c>
       <c r="D3" t="n">
-        <v>10823000</v>
+        <v>9773000</v>
       </c>
       <c r="E3" t="n">
-        <v>446990000</v>
+        <v>449524000</v>
       </c>
       <c r="F3" t="n">
-        <v>453771000</v>
+        <v>457260000</v>
       </c>
       <c r="G3" t="n">
-        <v>398349000</v>
+        <v>399213000</v>
       </c>
       <c r="H3" t="n">
-        <v>446990000</v>
+        <v>449524000</v>
       </c>
       <c r="I3" t="n">
-        <v>6266000</v>
+        <v>5306000</v>
       </c>
       <c r="J3" t="n">
-        <v>449214000</v>
+        <v>452793000</v>
       </c>
       <c r="K3" t="n">
-        <v>449214000</v>
+        <v>452793000</v>
       </c>
       <c r="L3" t="n">
-        <v>430050000</v>
+        <v>438032000</v>
       </c>
       <c r="M3" t="n">
-        <v>-19164000</v>
+        <v>-14761000</v>
       </c>
       <c r="N3" t="n">
-        <v>449214000</v>
+        <v>452793000</v>
       </c>
       <c r="O3" t="n">
-        <v>-452985000</v>
+        <v>-450087000</v>
       </c>
       <c r="P3" t="n">
         <v>750821000</v>
@@ -1735,127 +1681,129 @@
         <v>12322000</v>
       </c>
       <c r="S3" t="n">
-        <v>61484000</v>
+        <v>95091000</v>
       </c>
       <c r="T3" t="n">
-        <v>3010000</v>
+        <v>3957000</v>
       </c>
       <c r="U3" t="n">
-        <v>3010000</v>
+        <v>3957000</v>
       </c>
       <c r="V3" t="n">
-        <v>3010000</v>
+        <v>3957000</v>
       </c>
       <c r="W3" t="n">
-        <v>58474000</v>
+        <v>91134000</v>
       </c>
       <c r="X3" t="n">
-        <v>7813000</v>
+        <v>5816000</v>
       </c>
       <c r="Y3" t="n">
-        <v>3256000</v>
+        <v>1349000</v>
       </c>
       <c r="Z3" t="n">
-        <v>4557000</v>
+        <v>4467000</v>
       </c>
       <c r="AA3" t="n">
-        <v>41141000</v>
+        <v>71467000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11773000</v>
+        <v>38675000</v>
       </c>
       <c r="AC3" t="n">
-        <v>282000</v>
+        <v>3875000</v>
       </c>
       <c r="AD3" t="n">
-        <v>29086000</v>
+        <v>28917000</v>
       </c>
       <c r="AE3" t="n">
-        <v>491534000</v>
+        <v>533123000</v>
       </c>
       <c r="AF3" t="n">
-        <v>34711000</v>
+        <v>42776000</v>
       </c>
       <c r="AG3" t="n">
-        <v>141000</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>24960000</v>
+        <v>32629000</v>
       </c>
       <c r="AI3" t="n">
-        <v>24960000</v>
+        <v>32629000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>77000</v>
+        <v>174000</v>
       </c>
       <c r="AK3" t="n">
-        <v>77000</v>
+        <v>174000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2224000</v>
+        <v>3269000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2224000</v>
+        <v>3269000</v>
       </c>
       <c r="AN3" t="n">
-        <v>7309000</v>
+        <v>6704000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-3868000</v>
+        <v>-3083000</v>
       </c>
       <c r="AP3" t="n">
-        <v>11177000</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
+        <v>9787000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6704000</v>
+      </c>
       <c r="AR3" t="n">
-        <v>5476000</v>
+        <v>4899000</v>
       </c>
       <c r="AS3" t="n">
-        <v>5701000</v>
+        <v>4888000</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>456823000</v>
+        <v>490347000</v>
       </c>
       <c r="AV3" t="n">
-        <v>4294000</v>
+        <v>14857000</v>
       </c>
       <c r="AW3" t="n">
-        <v>15704000</v>
+        <v>14767000</v>
       </c>
       <c r="AX3" t="n">
-        <v>28704000</v>
+        <v>12965000</v>
       </c>
       <c r="AY3" t="n">
-        <v>16550000</v>
+        <v>82273000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-14860000</v>
+        <v>-9316000</v>
       </c>
       <c r="BA3" t="n">
-        <v>31410000</v>
+        <v>91589000</v>
       </c>
       <c r="BB3" t="n">
-        <v>391571000</v>
+        <v>365485000</v>
       </c>
       <c r="BC3" t="n">
-        <v>85373000</v>
+        <v>42657000</v>
       </c>
       <c r="BD3" t="n">
-        <v>306198000</v>
+        <v>322828000</v>
       </c>
       <c r="BE3" t="n">
-        <v>267272000</v>
+        <v>263352000</v>
       </c>
       <c r="BF3" t="n">
-        <v>38926000</v>
+        <v>59476000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1419610000</v>
@@ -1864,40 +1812,40 @@
         <v>1419610000</v>
       </c>
       <c r="D4" t="n">
-        <v>9773000</v>
+        <v>10823000</v>
       </c>
       <c r="E4" t="n">
-        <v>449524000</v>
+        <v>446990000</v>
       </c>
       <c r="F4" t="n">
-        <v>457260000</v>
+        <v>453771000</v>
       </c>
       <c r="G4" t="n">
-        <v>399213000</v>
+        <v>398349000</v>
       </c>
       <c r="H4" t="n">
-        <v>449524000</v>
+        <v>446990000</v>
       </c>
       <c r="I4" t="n">
-        <v>5306000</v>
+        <v>6266000</v>
       </c>
       <c r="J4" t="n">
-        <v>452793000</v>
+        <v>449214000</v>
       </c>
       <c r="K4" t="n">
-        <v>452793000</v>
+        <v>449214000</v>
       </c>
       <c r="L4" t="n">
-        <v>438032000</v>
+        <v>430050000</v>
       </c>
       <c r="M4" t="n">
-        <v>-14761000</v>
+        <v>-19164000</v>
       </c>
       <c r="N4" t="n">
-        <v>452793000</v>
+        <v>449214000</v>
       </c>
       <c r="O4" t="n">
-        <v>-450087000</v>
+        <v>-452985000</v>
       </c>
       <c r="P4" t="n">
         <v>750821000</v>
@@ -1909,129 +1857,127 @@
         <v>12322000</v>
       </c>
       <c r="S4" t="n">
-        <v>95091000</v>
+        <v>61484000</v>
       </c>
       <c r="T4" t="n">
-        <v>3957000</v>
+        <v>3010000</v>
       </c>
       <c r="U4" t="n">
-        <v>3957000</v>
+        <v>3010000</v>
       </c>
       <c r="V4" t="n">
-        <v>3957000</v>
+        <v>3010000</v>
       </c>
       <c r="W4" t="n">
-        <v>91134000</v>
+        <v>58474000</v>
       </c>
       <c r="X4" t="n">
-        <v>5816000</v>
+        <v>7813000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1349000</v>
+        <v>3256000</v>
       </c>
       <c r="Z4" t="n">
-        <v>4467000</v>
+        <v>4557000</v>
       </c>
       <c r="AA4" t="n">
-        <v>71467000</v>
+        <v>41141000</v>
       </c>
       <c r="AB4" t="n">
-        <v>38675000</v>
+        <v>11773000</v>
       </c>
       <c r="AC4" t="n">
-        <v>3875000</v>
+        <v>282000</v>
       </c>
       <c r="AD4" t="n">
-        <v>28917000</v>
+        <v>29086000</v>
       </c>
       <c r="AE4" t="n">
-        <v>533123000</v>
+        <v>491534000</v>
       </c>
       <c r="AF4" t="n">
-        <v>42776000</v>
+        <v>34711000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>141000</v>
       </c>
       <c r="AH4" t="n">
-        <v>32629000</v>
+        <v>24960000</v>
       </c>
       <c r="AI4" t="n">
-        <v>32629000</v>
+        <v>24960000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>174000</v>
+        <v>77000</v>
       </c>
       <c r="AK4" t="n">
-        <v>174000</v>
+        <v>77000</v>
       </c>
       <c r="AL4" t="n">
-        <v>3269000</v>
+        <v>2224000</v>
       </c>
       <c r="AM4" t="n">
-        <v>3269000</v>
+        <v>2224000</v>
       </c>
       <c r="AN4" t="n">
-        <v>6704000</v>
+        <v>7309000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-3083000</v>
+        <v>-3868000</v>
       </c>
       <c r="AP4" t="n">
-        <v>9787000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6704000</v>
-      </c>
+        <v>11177000</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>4899000</v>
+        <v>5476000</v>
       </c>
       <c r="AS4" t="n">
-        <v>4888000</v>
+        <v>5701000</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>490347000</v>
+        <v>456823000</v>
       </c>
       <c r="AV4" t="n">
-        <v>14857000</v>
+        <v>4294000</v>
       </c>
       <c r="AW4" t="n">
-        <v>14767000</v>
+        <v>15704000</v>
       </c>
       <c r="AX4" t="n">
-        <v>12965000</v>
+        <v>28704000</v>
       </c>
       <c r="AY4" t="n">
-        <v>82273000</v>
+        <v>16550000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-9316000</v>
+        <v>-14860000</v>
       </c>
       <c r="BA4" t="n">
-        <v>91589000</v>
+        <v>31410000</v>
       </c>
       <c r="BB4" t="n">
-        <v>365485000</v>
+        <v>391571000</v>
       </c>
       <c r="BC4" t="n">
-        <v>42657000</v>
+        <v>85373000</v>
       </c>
       <c r="BD4" t="n">
-        <v>322828000</v>
+        <v>306198000</v>
       </c>
       <c r="BE4" t="n">
-        <v>263352000</v>
+        <v>267272000</v>
       </c>
       <c r="BF4" t="n">
-        <v>59476000</v>
+        <v>38926000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1419610000</v>
@@ -2040,40 +1986,40 @@
         <v>1419610000</v>
       </c>
       <c r="D5" t="n">
-        <v>6505000</v>
+        <v>7341000</v>
       </c>
       <c r="E5" t="n">
-        <v>415492000</v>
+        <v>429358000</v>
       </c>
       <c r="F5" t="n">
-        <v>418983000</v>
+        <v>435220000</v>
       </c>
       <c r="G5" t="n">
-        <v>374544000</v>
+        <v>403021000</v>
       </c>
       <c r="H5" t="n">
-        <v>415492000</v>
+        <v>429358000</v>
       </c>
       <c r="I5" t="n">
-        <v>6505000</v>
+        <v>2629000</v>
       </c>
       <c r="J5" t="n">
-        <v>418983000</v>
+        <v>430508000</v>
       </c>
       <c r="K5" t="n">
-        <v>418983000</v>
+        <v>430508000</v>
       </c>
       <c r="L5" t="n">
-        <v>410422000</v>
+        <v>406792000</v>
       </c>
       <c r="M5" t="n">
-        <v>-8561000</v>
+        <v>-23716000</v>
       </c>
       <c r="N5" t="n">
-        <v>418983000</v>
+        <v>430508000</v>
       </c>
       <c r="O5" t="n">
-        <v>-449785000</v>
+        <v>-458764000</v>
       </c>
       <c r="P5" t="n">
         <v>750821000</v>
@@ -2085,120 +2031,290 @@
         <v>12322000</v>
       </c>
       <c r="S5" t="n">
-        <v>172331000</v>
+        <v>105767000</v>
       </c>
       <c r="T5" t="n">
-        <v>5410000</v>
+        <v>746000</v>
       </c>
       <c r="U5" t="n">
-        <v>5410000</v>
+        <v>746000</v>
       </c>
       <c r="V5" t="n">
-        <v>5410000</v>
+        <v>746000</v>
       </c>
       <c r="W5" t="n">
-        <v>166921000</v>
+        <v>105021000</v>
       </c>
       <c r="X5" t="n">
-        <v>1095000</v>
+        <v>6595000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1095000</v>
+        <v>1883000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4712000</v>
       </c>
       <c r="AA5" t="n">
-        <v>76428000</v>
+        <v>33639000</v>
       </c>
       <c r="AB5" t="n">
-        <v>37740000</v>
+        <v>14960000</v>
       </c>
       <c r="AC5" t="n">
-        <v>7986000</v>
+        <v>292000</v>
       </c>
       <c r="AD5" t="n">
-        <v>30702000</v>
+        <v>18387000</v>
       </c>
       <c r="AE5" t="n">
-        <v>582753000</v>
+        <v>512559000</v>
       </c>
       <c r="AF5" t="n">
-        <v>41288000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>4517000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>105000</v>
+      </c>
       <c r="AH5" t="n">
-        <v>28616000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>28616000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>464000</v>
+        <v>52000</v>
       </c>
       <c r="AK5" t="n">
-        <v>464000</v>
+        <v>52000</v>
       </c>
       <c r="AL5" t="n">
-        <v>3491000</v>
+        <v>1150000</v>
       </c>
       <c r="AM5" t="n">
-        <v>3491000</v>
+        <v>1150000</v>
       </c>
       <c r="AN5" t="n">
-        <v>8717000</v>
+        <v>3210000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-2541000</v>
+        <v>-4698000</v>
       </c>
       <c r="AP5" t="n">
-        <v>11258000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>8717000</v>
-      </c>
+        <v>7908000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>4941000</v>
+        <v>5701000</v>
       </c>
       <c r="AS5" t="n">
-        <v>6317000</v>
+        <v>2207000</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>541465000</v>
+        <v>508042000</v>
       </c>
       <c r="AV5" t="n">
-        <v>65340000</v>
+        <v>73946000</v>
       </c>
       <c r="AW5" t="n">
-        <v>14118000</v>
+        <v>11569000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1878000</v>
+        <v>44294000</v>
       </c>
       <c r="AY5" t="n">
-        <v>84833000</v>
+        <v>4833000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-5163000</v>
+        <v>-14030000</v>
       </c>
       <c r="BA5" t="n">
-        <v>89996000</v>
+        <v>18863000</v>
       </c>
       <c r="BB5" t="n">
-        <v>375296000</v>
+        <v>373400000</v>
       </c>
       <c r="BC5" t="n">
-        <v>63237000</v>
+        <v>55250000</v>
       </c>
       <c r="BD5" t="n">
-        <v>312059000</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
+        <v>318150000</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>289900000</v>
+      </c>
       <c r="BF5" t="n">
-        <v>312059000</v>
+        <v>28250000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1419610000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1419610000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11078000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>399710000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>404204000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>370545000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>399710000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6584000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>399710000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>399710000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>374735000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-24975000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>399710000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-472975000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>750821000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>12322000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>12322000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>69632000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5543000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5543000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5543000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>64089000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5535000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1041000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4494000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>32248000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>13830000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>405000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>18013000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>444367000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>9733000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>51000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>51000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>9636000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-4686000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>14322000</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>5319000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9003000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>434634000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>57714000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>9169000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>23773000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9623000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-14254000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>23877000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>334355000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>67473000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>266882000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>237294000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>29588000</v>
       </c>
     </row>
   </sheetData>
@@ -2212,7 +2328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP5"/>
+  <dimension ref="A1:AP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2424,458 +2540,506 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-6538000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>-145000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>186219000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>226023000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6162000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-45966000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-2569000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-608000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>-37004000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>11299000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-48158000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>249860000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-298018000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>-145000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>-145000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-6393000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-2103000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="n">
-        <v>2064000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>76327000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-7045000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-68087000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>869000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-11882000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>3761000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1126000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2635000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>-9217000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>-900000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-900000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>-3952000</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>17000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-30060000</v>
+        <v>-19572000</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4467000</v>
       </c>
       <c r="E3" t="n">
-        <v>-500000</v>
+        <v>-89000</v>
       </c>
       <c r="F3" t="n">
-        <v>226023000</v>
+        <v>322828000</v>
       </c>
       <c r="G3" t="n">
-        <v>322828000</v>
+        <v>312059000</v>
       </c>
       <c r="H3" t="n">
-        <v>5179000</v>
+        <v>25416000</v>
       </c>
       <c r="I3" t="n">
-        <v>-101984000</v>
+        <v>-14647000</v>
       </c>
       <c r="J3" t="n">
-        <v>-2956000</v>
+        <v>2792000</v>
       </c>
       <c r="K3" t="n">
-        <v>-816000</v>
+        <v>-624000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4467000</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4467000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4467000</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>-69468000</v>
+        <v>2044000</v>
       </c>
       <c r="R3" t="n">
-        <v>10653000</v>
+        <v>2233000</v>
       </c>
       <c r="S3" t="n">
-        <v>-79621000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>174207000</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-253828000</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>-500000</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
+        <v>-89000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
       <c r="AB3" t="n">
-        <v>-500000</v>
+        <v>-89000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-29560000</v>
+        <v>-19483000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-3899000</v>
+        <v>-4748000</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>-27071000</v>
+        <v>-15465000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-49385000</v>
+        <v>-62903000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-33014000</v>
+        <v>-2365000</v>
       </c>
       <c r="AI3" t="n">
-        <v>10777000</v>
+        <v>54504000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>44551000</v>
+        <v>-4701000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-9489000</v>
+        <v>-3511000</v>
       </c>
       <c r="AL3" t="n">
-        <v>4119000</v>
+        <v>2624000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1103000</v>
+        <v>525000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3016000</v>
+        <v>2099000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-7552000</v>
+        <v>-6640000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-19572000</v>
+        <v>-30060000</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>4467000</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-89000</v>
+        <v>-500000</v>
       </c>
       <c r="F4" t="n">
+        <v>226023000</v>
+      </c>
+      <c r="G4" t="n">
         <v>322828000</v>
       </c>
-      <c r="G4" t="n">
-        <v>312059000</v>
-      </c>
       <c r="H4" t="n">
-        <v>25416000</v>
+        <v>5179000</v>
       </c>
       <c r="I4" t="n">
-        <v>-14647000</v>
+        <v>-101984000</v>
       </c>
       <c r="J4" t="n">
-        <v>2792000</v>
+        <v>-2956000</v>
       </c>
       <c r="K4" t="n">
-        <v>-624000</v>
+        <v>-816000</v>
       </c>
       <c r="L4" t="n">
-        <v>4467000</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4467000</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4467000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>2044000</v>
+        <v>-69468000</v>
       </c>
       <c r="R4" t="n">
-        <v>2233000</v>
+        <v>10653000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-79621000</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>174207000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-253828000</v>
       </c>
       <c r="V4" t="n">
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-89000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+        <v>-500000</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>-89000</v>
+        <v>-500000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-19483000</v>
+        <v>-29560000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-4748000</v>
+        <v>-3899000</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>-15465000</v>
+        <v>-27071000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-62903000</v>
+        <v>-49385000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-2365000</v>
+        <v>-33014000</v>
       </c>
       <c r="AI4" t="n">
-        <v>54504000</v>
+        <v>10777000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-4701000</v>
+        <v>44551000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-3511000</v>
+        <v>-9489000</v>
       </c>
       <c r="AL4" t="n">
-        <v>2624000</v>
+        <v>4119000</v>
       </c>
       <c r="AM4" t="n">
-        <v>525000</v>
+        <v>1103000</v>
       </c>
       <c r="AN4" t="n">
-        <v>2099000</v>
+        <v>3016000</v>
       </c>
       <c r="AO4" t="n">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>-6640000</v>
+        <v>-7552000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>55708000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
+        <v>-6538000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>-2007000</v>
+        <v>-145000</v>
       </c>
       <c r="F5" t="n">
-        <v>312059000</v>
+        <v>186219000</v>
       </c>
       <c r="G5" t="n">
-        <v>293029000</v>
+        <v>226023000</v>
       </c>
       <c r="H5" t="n">
-        <v>-7546000</v>
+        <v>6162000</v>
       </c>
       <c r="I5" t="n">
-        <v>26576000</v>
+        <v>-45966000</v>
       </c>
       <c r="J5" t="n">
-        <v>-1339000</v>
+        <v>-2569000</v>
       </c>
       <c r="K5" t="n">
-        <v>-323000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
+        <v>-608000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>-29800000</v>
+        <v>-37004000</v>
       </c>
       <c r="R5" t="n">
-        <v>2137000</v>
+        <v>11299000</v>
       </c>
       <c r="S5" t="n">
-        <v>-29032000</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+        <v>-48158000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>249860000</v>
+      </c>
       <c r="U5" t="n">
-        <v>-29032000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-900000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-900000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
+        <v>-298018000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-2005000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2000</v>
-      </c>
+        <v>-145000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-2007000</v>
+        <v>-145000</v>
       </c>
       <c r="AC5" t="n">
-        <v>57715000</v>
+        <v>-6393000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3952000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-3952000</v>
-      </c>
+        <v>-2103000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>17850000</v>
+        <v>2064000</v>
       </c>
       <c r="AG5" t="n">
-        <v>15812000</v>
+        <v>76327000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-21379000</v>
+        <v>-7045000</v>
       </c>
       <c r="AI5" t="n">
-        <v>22392000</v>
+        <v>-68087000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1025000</v>
+        <v>869000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1827000</v>
+        <v>-11882000</v>
       </c>
       <c r="AL5" t="n">
-        <v>2336000</v>
+        <v>3761000</v>
       </c>
       <c r="AM5" t="n">
-        <v>506000</v>
+        <v>1126000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1830000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>17000</v>
-      </c>
+        <v>2635000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>23041000</v>
+        <v>-9217000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-46690000</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>-3261000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>266882000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>186219000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-9588000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>90251000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1077000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-379000</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>134757000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9182000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>128836000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>128836000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>-3261000</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>-3261000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-43429000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-277000</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>-59899000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-82859000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1995000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8996000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>11969000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-7488000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2931000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1123000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1808000</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>-14039000</v>
       </c>
     </row>
   </sheetData>
@@ -2889,7 +3053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EG2"/>
+  <dimension ref="A1:EI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3330,250 +3494,260 @@
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
+          <t>freeCashflow</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>operatingCashflow</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3650,7 +3824,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Ms. Yee Ling  Lok', 'age': 68, 'title': 'Executive Director', 'yearBorn': 1957, 'fiscalYear': 2025, 'totalPay': 830388, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jiong  Gu', 'age': 53, 'title': 'Executive Director', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 612657, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Tsz Kwan  Leung', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Ms. Yee Ling  Lok', 'age': 68, 'title': 'Executive Director', 'yearBorn': 1957, 'fiscalYear': 2025, 'totalPay': 830472, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jiong  Gu', 'age': 53, 'title': 'Executive Director', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 612719, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Tsz Kwan  Leung', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3668,28 +3842,28 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0.153</v>
+        <v>0.191</v>
       </c>
       <c r="U2" t="n">
-        <v>0.154</v>
+        <v>0.191</v>
       </c>
       <c r="V2" t="n">
-        <v>0.154</v>
+        <v>0.182</v>
       </c>
       <c r="W2" t="n">
-        <v>0.164</v>
+        <v>0.191</v>
       </c>
       <c r="X2" t="n">
-        <v>0.153</v>
+        <v>0.191</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.154</v>
+        <v>0.191</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.154</v>
+        <v>0.182</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.164</v>
+        <v>0.191</v>
       </c>
       <c r="AB2" t="n">
         <v>1316390400</v>
@@ -3698,28 +3872,28 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.618</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AE2" t="n">
-        <v>1464000</v>
+        <v>924000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1464000</v>
+        <v>924000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1265533</v>
+        <v>1298600</v>
       </c>
       <c r="AH2" t="n">
-        <v>2078600</v>
+        <v>1391000</v>
       </c>
       <c r="AI2" t="n">
-        <v>2078600</v>
+        <v>1391000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.158</v>
+        <v>0.182</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.163</v>
+        <v>0.185</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -3728,10 +3902,10 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>231396432</v>
+        <v>259788624</v>
       </c>
       <c r="AO2" t="n">
-        <v>217200330</v>
+        <v>259788630</v>
       </c>
       <c r="AP2" t="n">
         <v>0.115</v>
@@ -3746,13 +3920,13 @@
         <v>0.095</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.5052916</v>
+        <v>1.6899899</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.20964</v>
+        <v>0.19554</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.27941</v>
+        <v>0.270205</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -3769,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-49382568</v>
+        <v>-12472710</v>
       </c>
       <c r="BB2" t="n">
         <v>-0.09245</v>
@@ -3790,10 +3964,10 @@
         <v>1419610000</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.326596</v>
+        <v>0.32662898</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.49908757</v>
+        <v>0.5602687</v>
       </c>
       <c r="BJ2" t="n">
         <v>1767139200</v>
@@ -3811,16 +3985,16 @@
         <v>-0.01</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.321</v>
+        <v>-0.081</v>
       </c>
       <c r="BP2" t="n">
-        <v>2.294</v>
+        <v>0.582</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.28571427</v>
+        <v>0.525</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27294624</v>
+        <v>0.2568333</v>
       </c>
       <c r="BS2" t="n">
         <v>0.025</v>
@@ -3834,7 +4008,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>0.163</v>
+        <v>0.183</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -3848,7 +4022,7 @@
         <v>0.188</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-21529000</v>
+        <v>-21424000</v>
       </c>
       <c r="CA2" t="n">
         <v>11078000</v>
@@ -3878,60 +4052,60 @@
         <v>5880000</v>
       </c>
       <c r="CJ2" t="n">
+        <v>-32226376</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>-43429000</v>
+      </c>
+      <c r="CL2" t="n">
         <v>0.217</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CM2" t="n">
         <v>0.03825</v>
       </c>
-      <c r="CL2" t="n">
-        <v>-0.14005</v>
-      </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
+        <v>-0.13937001</v>
+      </c>
+      <c r="CO2" t="n">
         <v>-0.5388500000000001</v>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>0953.HK</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CW2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
-      </c>
-      <c r="CV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>15</v>
       </c>
       <c r="CX2" t="b">
         <v>0</v>
@@ -3943,11 +4117,11 @@
         <v>1264987800000</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.010000005</v>
+        <v>-0.008000001</v>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>0.154 - 0.164</t>
+          <t>0.182 - 0.191</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
@@ -3956,13 +4130,13 @@
         </is>
       </c>
       <c r="DD2" t="n">
-        <v>1265533</v>
+        <v>1298600</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.048</v>
+        <v>0.06799999599999999</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.4173913</v>
+        <v>0.5913043</v>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
@@ -3970,13 +4144,13 @@
         </is>
       </c>
       <c r="DH2" t="n">
-        <v>-0.237</v>
+        <v>-0.21700001</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.5925</v>
+        <v>-0.5425</v>
       </c>
       <c r="DJ2" t="n">
-        <v>28.571426</v>
+        <v>52.499996</v>
       </c>
       <c r="DK2" t="n">
         <v>1742910236</v>
@@ -3991,78 +4165,84 @@
         <v>-0.01</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.046639994</v>
+        <v>-0.012539998</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0.2224766</v>
+        <v>-0.06413009</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.11641</v>
+        <v>-0.08720499</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.41662788</v>
-      </c>
-      <c r="DS2" t="inlineStr">
+        <v>-0.3227364</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DU2" t="inlineStr">
         <is>
           <t>Shaw Brothers Holdings Limited</t>
         </is>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>SHAW BROTHERS</t>
         </is>
       </c>
-      <c r="DU2" t="n">
-        <v>6.535951</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.163</v>
-      </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DY2" t="n">
-        <v>1780387084</v>
+      <c r="DX2" t="n">
+        <v>1781769599</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>finmb_84586229</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>finmb_84586229</t>
+          <t>Asia/Hong_Kong</t>
         </is>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="ED2" t="n">
+      <c r="EC2" t="n">
         <v>28800000</v>
       </c>
-      <c r="EE2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="inlineStr"/>
+      <c r="EE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-4.1884823</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
